--- a/五年规划.xlsx
+++ b/五年规划.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="月度现金流" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="理财建议" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="¥#,##0;(¥#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,11 +89,6 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="15"/>
     </font>
   </fonts>
   <fills count="12">
@@ -173,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,42 +267,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4958,414 +4916,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
-        <is>
-          <t>家庭理财与风险管理建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="38" t="inlineStr">
-        <is>
-          <t>一、应急备用金</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>建议金额</t>
-        </is>
-      </c>
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>约¥50,000（孩子出生后6个月家庭开销）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="41" t="inlineStr">
-        <is>
-          <t>存放方式</t>
-        </is>
-      </c>
-      <c r="B5" s="42" t="inlineStr">
-        <is>
-          <t>货币基金（如余额宝）或活期存款，随时可取</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="B6" s="44" t="inlineStr">
-        <is>
-          <t>存款38万远超应急需求，可将5万单独存入货币基金专户</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>注意事项</t>
-        </is>
-      </c>
-      <c r="B7" s="42" t="inlineStr">
-        <is>
-          <t>应急金不参与任何投资，保持流动性第一</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
-        <is>
-          <t>二、保险规划</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t>现状</t>
-        </is>
-      </c>
-      <c r="B10" s="46" t="inlineStr">
-        <is>
-          <t>目前仅有社保，商业保险保障不足</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="41" t="inlineStr">
-        <is>
-          <t>建议-双方各购</t>
-        </is>
-      </c>
-      <c r="B11" s="42" t="inlineStr">
-        <is>
-          <t>百万医疗险：约¥300-500/人/年，覆盖大额医疗</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="41" t="inlineStr">
-        <is>
-          <t>建议-双方各购</t>
-        </is>
-      </c>
-      <c r="B12" s="42" t="inlineStr">
-        <is>
-          <t>重疾险（消费型）：约¥1,500-3,000/人/年，保额50万+</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>建议-双方各购</t>
-        </is>
-      </c>
-      <c r="B13" s="48" t="inlineStr">
-        <is>
-          <t>定期寿险：约¥1,000-2,000/人/年，保额100万（有孩子后必备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="41" t="inlineStr">
-        <is>
-          <t>孩子保险</t>
-        </is>
-      </c>
-      <c r="B14" s="42" t="inlineStr">
-        <is>
-          <t>少儿医疗险：约¥200-300/年；重疾险可考虑¥1,000-2,000/年</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>年度保险预算</t>
-        </is>
-      </c>
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>合计约¥8,000-15,000/年，占年收入约2-4%，合理范围</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="38" t="inlineStr">
-        <is>
-          <t>三、存款投资建议（保守型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="41" t="inlineStr">
-        <is>
-          <t>原则</t>
-        </is>
-      </c>
-      <c r="B18" s="42" t="inlineStr">
-        <is>
-          <t>保守型：以保本为主，追求稳健收益，不炒股不投机</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="41" t="inlineStr">
-        <is>
-          <t>应急金（5万）</t>
-        </is>
-      </c>
-      <c r="B19" s="42" t="inlineStr">
-        <is>
-          <t>货币基金，年化约1.5-2.5%，随时可取</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="41" t="inlineStr">
-        <is>
-          <t>短期备用（10万）</t>
-        </is>
-      </c>
-      <c r="B20" s="42" t="inlineStr">
-        <is>
-          <t>银行定期存款或大额存单，1-3年期，年化约2-3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>中期理财（20万）</t>
-        </is>
-      </c>
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>国债/储蓄国债，3-5年期，年化约2.5-3.5%，安全性高</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="41" t="inlineStr">
-        <is>
-          <t>长期规划（剩余）</t>
-        </is>
-      </c>
-      <c r="B22" s="42" t="inlineStr">
-        <is>
-          <t>银行R2级理财产品，年化约3-4%，低风险</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="47" t="inlineStr">
-        <is>
-          <t>预期综合收益</t>
-        </is>
-      </c>
-      <c r="B23" s="48" t="inlineStr">
-        <is>
-          <t>约2.5-3.5%/年，38万存款年收益约¥9,500-13,300</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t>四、孩子教育金规划</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="41" t="inlineStr">
-        <is>
-          <t>目标</t>
-        </is>
-      </c>
-      <c r="B26" s="42" t="inlineStr">
-        <is>
-          <t>为孩子准备大学教育金，目标¥20-30万（18年后）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="41" t="inlineStr">
-        <is>
-          <t>建议方式</t>
-        </is>
-      </c>
-      <c r="B27" s="42" t="inlineStr">
-        <is>
-          <t>每月定投¥500-1,000至货币基金或低风险理财</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>18年积累</t>
-        </is>
-      </c>
-      <c r="B28" s="44" t="inlineStr">
-        <is>
-          <t>每月¥800，年化3%，18年后约¥22万</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="47" t="inlineStr">
-        <is>
-          <t>启动时间</t>
-        </is>
-      </c>
-      <c r="B29" s="48" t="inlineStr">
-        <is>
-          <t>孩子出生后即开始，越早越好</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="38" t="inlineStr">
-        <is>
-          <t>五、5年财务目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="41" t="inlineStr">
-        <is>
-          <t>2026年末目标</t>
-        </is>
-      </c>
-      <c r="B32" s="42" t="inlineStr">
-        <is>
-          <t>完成结婚，累计储蓄约¥55万</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="41" t="inlineStr">
-        <is>
-          <t>2027年末目标</t>
-        </is>
-      </c>
-      <c r="B33" s="42" t="inlineStr">
-        <is>
-          <t>迎接宝宝，累计储蓄约¥82万</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="43" t="inlineStr">
-        <is>
-          <t>2028年末目标</t>
-        </is>
-      </c>
-      <c r="B34" s="44" t="inlineStr">
-        <is>
-          <t>家庭稳定运转，累计储蓄约¥107万</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="43" t="inlineStr">
-        <is>
-          <t>2029年末目标</t>
-        </is>
-      </c>
-      <c r="B35" s="44" t="inlineStr">
-        <is>
-          <t>持续积累，累计储蓄约¥132万</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="43" t="inlineStr">
-        <is>
-          <t>2030年末目标</t>
-        </is>
-      </c>
-      <c r="B36" s="44" t="inlineStr">
-        <is>
-          <t>5年规划完成，累计储蓄约¥158万</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="47" t="inlineStr">
-        <is>
-          <t>核心建议</t>
-        </is>
-      </c>
-      <c r="B37" s="48" t="inlineStr">
-        <is>
-          <t>收入稳定、无负债、储蓄率高，财务状况优秀！建议尽早配置保险</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="B35:F35"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/五年规划.xlsx
+++ b/五年规划.xlsx
@@ -35,13 +35,13 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00000000"/>
+      <color rgb="002D3748"/>
     </font>
     <font>
       <b val="1"/>
     </font>
     <font>
-      <color rgb="000000FF"/>
+      <color rgb="002B6CB0"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +49,7 @@
       <sz val="16"/>
     </font>
     <font>
-      <color rgb="00595959"/>
+      <color rgb="00718096"/>
       <sz val="10"/>
     </font>
     <font>
@@ -63,7 +63,7 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00595959"/>
+      <color rgb="00718096"/>
       <sz val="9"/>
     </font>
     <font>
@@ -77,26 +77,26 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="002D3748"/>
       <sz val="10"/>
     </font>
     <font>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="002F855A"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="002D3748"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="00718096"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -105,52 +105,47 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="002D3748"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F7FAFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DEEAF1"/>
+        <fgColor rgb="00EDF2F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="004A90D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="00EBF4FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FDE8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,37 +178,37 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -229,16 +224,16 @@
     <xf numFmtId="164" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">

--- a/五年规划.xlsx
+++ b/五年规划.xlsx
@@ -770,12 +770,24 @@
           <t>每月税后可支配收入</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="6" t="n"/>
+      <c r="D6" s="8" t="n">
+        <v>202604</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>27500</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>202704</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>202804</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>31000</v>
+      </c>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="8" t="n"/>
@@ -791,12 +803,24 @@
         <v>46000</v>
       </c>
       <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="6" t="n"/>
+      <c r="D7" s="8" t="n">
+        <v>202604</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>47500</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>202704</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>49000</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>202804</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>51000</v>
+      </c>
       <c r="J7" s="8" t="n"/>
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="8" t="n"/>
@@ -834,7 +858,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -859,7 +883,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
@@ -1085,7 +1109,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C20" s="7" t="inlineStr"/>
     </row>
@@ -1096,7 +1120,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -1111,7 +1135,7 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.031</v>
+        <v>0.021</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>

--- a/五年规划.xlsx
+++ b/五年规划.xlsx
@@ -19,10 +19,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="¥#,##0;(¥#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="164" formatCode="¥#,##0;[Red]-¥#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +90,9 @@
     <font>
       <b val="1"/>
       <color rgb="002D3748"/>
+    </font>
+    <font>
+      <color rgb="00C53030"/>
     </font>
     <font>
       <i val="1"/>
@@ -234,10 +237,7 @@
     <xf numFmtId="164" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -250,6 +250,9 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -645,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1271,7 +1274,7 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>年初余额</t>
+          <t>年初存款</t>
         </is>
       </c>
       <c r="B30" s="15">
@@ -1279,19 +1282,19 @@
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>B50</f>
+        <f>B49</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>C50</f>
+        <f>C49</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>D50</f>
+        <f>D49</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>E50</f>
+        <f>E49</f>
         <v/>
       </c>
       <c r="H30" s="15">
@@ -1299,19 +1302,19 @@
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>H50</f>
+        <f>H49</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>I50</f>
+        <f>I49</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>J50</f>
+        <f>J49</f>
         <v/>
       </c>
       <c r="L30" s="16">
-        <f>K50</f>
+        <f>K49</f>
         <v/>
       </c>
     </row>
@@ -1790,284 +1793,356 @@
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  【特殊支出】</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="18" t="n"/>
-      <c r="H43" s="18" t="n"/>
-      <c r="I43" s="18" t="n"/>
-      <c r="J43" s="18" t="n"/>
-      <c r="K43" s="18" t="n"/>
-      <c r="L43" s="18" t="n"/>
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  结婚</t>
+        </is>
+      </c>
+      <c r="B43" s="20">
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2026,月度现金流!L:L,"结婚支出")</f>
+        <v/>
+      </c>
+      <c r="C43" s="20">
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2027,月度现金流!L:L,"结婚支出")</f>
+        <v/>
+      </c>
+      <c r="D43" s="20">
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2028,月度现金流!L:L,"结婚支出")</f>
+        <v/>
+      </c>
+      <c r="E43" s="20">
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2029,月度现金流!L:L,"结婚支出")</f>
+        <v/>
+      </c>
+      <c r="F43" s="20">
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2030,月度现金流!L:L,"结婚支出")</f>
+        <v/>
+      </c>
+      <c r="H43" s="20">
+        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2026,'月度现金流（买房）'!L:L,"结婚支出")</f>
+        <v/>
+      </c>
+      <c r="I43" s="20">
+        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2027,'月度现金流（买房）'!L:L,"结婚支出")</f>
+        <v/>
+      </c>
+      <c r="J43" s="20">
+        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2028,'月度现金流（买房）'!L:L,"结婚支出")</f>
+        <v/>
+      </c>
+      <c r="K43" s="20">
+        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2029,'月度现金流（买房）'!L:L,"结婚支出")</f>
+        <v/>
+      </c>
+      <c r="L43" s="20">
+        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2030,'月度现金流（买房）'!L:L,"结婚支出")</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    结婚</t>
+          <t xml:space="preserve">  产检及分娩</t>
         </is>
       </c>
       <c r="B44" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2026,月度现金流!L:L,"结婚支出")</f>
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2026,月度现金流!L:L,"孕产费用")</f>
         <v/>
       </c>
       <c r="C44" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2027,月度现金流!L:L,"结婚支出")</f>
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2027,月度现金流!L:L,"孕产费用")</f>
         <v/>
       </c>
       <c r="D44" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2028,月度现金流!L:L,"结婚支出")</f>
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2028,月度现金流!L:L,"孕产费用")</f>
         <v/>
       </c>
       <c r="E44" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2029,月度现金流!L:L,"结婚支出")</f>
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2029,月度现金流!L:L,"孕产费用")</f>
         <v/>
       </c>
       <c r="F44" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2030,月度现金流!L:L,"结婚支出")</f>
+        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2030,月度现金流!L:L,"孕产费用")</f>
         <v/>
       </c>
       <c r="H44" s="20">
-        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2026,'月度现金流（买房）'!L:L,"结婚支出")</f>
+        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2026,'月度现金流（买房）'!L:L,"孕产费用")</f>
         <v/>
       </c>
       <c r="I44" s="20">
-        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2027,'月度现金流（买房）'!L:L,"结婚支出")</f>
+        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2027,'月度现金流（买房）'!L:L,"孕产费用")</f>
         <v/>
       </c>
       <c r="J44" s="20">
-        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2028,'月度现金流（买房）'!L:L,"结婚支出")</f>
+        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2028,'月度现金流（买房）'!L:L,"孕产费用")</f>
         <v/>
       </c>
       <c r="K44" s="20">
-        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2029,'月度现金流（买房）'!L:L,"结婚支出")</f>
+        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2029,'月度现金流（买房）'!L:L,"孕产费用")</f>
         <v/>
       </c>
       <c r="L44" s="20">
-        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2030,'月度现金流（买房）'!L:L,"结婚支出")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    产检及分娩</t>
-        </is>
-      </c>
-      <c r="B45" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2026,月度现金流!L:L,"孕产费用")</f>
-        <v/>
-      </c>
-      <c r="C45" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2027,月度现金流!L:L,"孕产费用")</f>
-        <v/>
-      </c>
-      <c r="D45" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2028,月度现金流!L:L,"孕产费用")</f>
-        <v/>
-      </c>
-      <c r="E45" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2029,月度现金流!L:L,"孕产费用")</f>
-        <v/>
-      </c>
-      <c r="F45" s="20">
-        <f>SUMIFS(月度现金流!K:K,月度现金流!B:B,2030,月度现金流!L:L,"孕产费用")</f>
-        <v/>
-      </c>
-      <c r="H45" s="20">
-        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2026,'月度现金流（买房）'!L:L,"孕产费用")</f>
-        <v/>
-      </c>
-      <c r="I45" s="20">
-        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2027,'月度现金流（买房）'!L:L,"孕产费用")</f>
-        <v/>
-      </c>
-      <c r="J45" s="20">
-        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2028,'月度现金流（买房）'!L:L,"孕产费用")</f>
-        <v/>
-      </c>
-      <c r="K45" s="20">
-        <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2029,'月度现金流（买房）'!L:L,"孕产费用")</f>
-        <v/>
-      </c>
-      <c r="L45" s="20">
         <f>SUMIFS('月度现金流（买房）'!K:K,'月度现金流（买房）'!B:B,2030,'月度现金流（买房）'!L:L,"孕产费用")</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="28" customHeight="1">
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>* 特殊支出数据来源：月度现金流汇总；结婚（2026年5月）及孕产费用（2027年9月）均为一次性支出</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="H45" s="18" t="n"/>
+      <c r="I45" s="18" t="n"/>
+      <c r="J45" s="18" t="n"/>
+      <c r="K45" s="18" t="n"/>
+      <c r="L45" s="18" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>* 特殊支出数据来源：月度现金流汇总；结婚（2026年5月）及孕产费用（2027年9月）均为一次性支出</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="n"/>
-      <c r="C46" s="18" t="n"/>
-      <c r="D46" s="18" t="n"/>
-      <c r="E46" s="18" t="n"/>
-      <c r="F46" s="18" t="n"/>
-      <c r="H46" s="18" t="n"/>
-      <c r="I46" s="18" t="n"/>
-      <c r="J46" s="18" t="n"/>
-      <c r="K46" s="18" t="n"/>
-      <c r="L46" s="18" t="n"/>
+          <t>支出小计</t>
+        </is>
+      </c>
+      <c r="B46" s="25">
+        <f>SUM(B37:B40)+SUM(B43:B44)</f>
+        <v/>
+      </c>
+      <c r="C46" s="25">
+        <f>SUM(C37:C40)+SUM(C43:C44)</f>
+        <v/>
+      </c>
+      <c r="D46" s="25">
+        <f>SUM(D37:D40)+SUM(D43:D44)</f>
+        <v/>
+      </c>
+      <c r="E46" s="25">
+        <f>SUM(E37:E40)+SUM(E43:E44)</f>
+        <v/>
+      </c>
+      <c r="F46" s="25">
+        <f>SUM(F37:F40)+SUM(F43:F44)</f>
+        <v/>
+      </c>
+      <c r="H46" s="25">
+        <f>SUM(H37:H40)+H41+H42+SUM(H43:H44)</f>
+        <v/>
+      </c>
+      <c r="I46" s="25">
+        <f>SUM(I37:I40)+I41+I42+SUM(I43:I44)</f>
+        <v/>
+      </c>
+      <c r="J46" s="25">
+        <f>SUM(J37:J40)+J41+J42+SUM(J43:J44)</f>
+        <v/>
+      </c>
+      <c r="K46" s="25">
+        <f>SUM(K37:K40)+K41+K42+SUM(K43:K44)</f>
+        <v/>
+      </c>
+      <c r="L46" s="25">
+        <f>SUM(L37:L40)+L41+L42+SUM(L43:L44)</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>支出小计</t>
-        </is>
-      </c>
-      <c r="B47" s="26">
-        <f>SUM(B37:B40)+SUM(B44:B45)</f>
-        <v/>
-      </c>
-      <c r="C47" s="26">
-        <f>SUM(C37:C40)+SUM(C44:C45)</f>
-        <v/>
-      </c>
-      <c r="D47" s="26">
-        <f>SUM(D37:D40)+SUM(D44:D45)</f>
-        <v/>
-      </c>
-      <c r="E47" s="26">
-        <f>SUM(E37:E40)+SUM(E44:E45)</f>
-        <v/>
-      </c>
-      <c r="F47" s="26">
-        <f>SUM(F37:F40)+SUM(F44:F45)</f>
-        <v/>
-      </c>
-      <c r="H47" s="26">
-        <f>SUM(H37:H40)+H41+H42+SUM(H44:H45)</f>
-        <v/>
-      </c>
-      <c r="I47" s="26">
-        <f>SUM(I37:I40)+I41+I42+SUM(I44:I45)</f>
-        <v/>
-      </c>
-      <c r="J47" s="26">
-        <f>SUM(J37:J40)+J41+J42+SUM(J44:J45)</f>
-        <v/>
-      </c>
-      <c r="K47" s="26">
-        <f>SUM(K37:K40)+K41+K42+SUM(K44:K45)</f>
-        <v/>
-      </c>
-      <c r="L47" s="26">
-        <f>SUM(L37:L40)+L41+L42+SUM(L44:L45)</f>
-        <v/>
-      </c>
+      <c r="A47" s="19" t="inlineStr"/>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="18" t="n"/>
+      <c r="J47" s="18" t="n"/>
+      <c r="K47" s="18" t="n"/>
+      <c r="L47" s="18" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="19" t="inlineStr"/>
-      <c r="B48" s="18" t="n"/>
-      <c r="C48" s="18" t="n"/>
-      <c r="D48" s="18" t="n"/>
-      <c r="E48" s="18" t="n"/>
-      <c r="F48" s="18" t="n"/>
-      <c r="H48" s="18" t="n"/>
-      <c r="I48" s="18" t="n"/>
-      <c r="J48" s="18" t="n"/>
-      <c r="K48" s="18" t="n"/>
-      <c r="L48" s="18" t="n"/>
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>年度结余（收入−支出）</t>
+        </is>
+      </c>
+      <c r="B48" s="27">
+        <f>B35-B46</f>
+        <v/>
+      </c>
+      <c r="C48" s="27">
+        <f>C35-C46</f>
+        <v/>
+      </c>
+      <c r="D48" s="27">
+        <f>D35-D46</f>
+        <v/>
+      </c>
+      <c r="E48" s="27">
+        <f>E35-E46</f>
+        <v/>
+      </c>
+      <c r="F48" s="27">
+        <f>F35-F46</f>
+        <v/>
+      </c>
+      <c r="H48" s="27">
+        <f>H35-H46</f>
+        <v/>
+      </c>
+      <c r="I48" s="27">
+        <f>I35-I46</f>
+        <v/>
+      </c>
+      <c r="J48" s="27">
+        <f>J35-J46</f>
+        <v/>
+      </c>
+      <c r="K48" s="27">
+        <f>K35-K46</f>
+        <v/>
+      </c>
+      <c r="L48" s="27">
+        <f>L35-L46</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>年度结余（收入−支出）</t>
-        </is>
-      </c>
-      <c r="B49" s="28">
-        <f>B35-B47</f>
-        <v/>
-      </c>
-      <c r="C49" s="28">
-        <f>C35-C47</f>
-        <v/>
-      </c>
-      <c r="D49" s="28">
-        <f>D35-D47</f>
-        <v/>
-      </c>
-      <c r="E49" s="28">
-        <f>E35-E47</f>
-        <v/>
-      </c>
-      <c r="F49" s="28">
-        <f>F35-F47</f>
-        <v/>
-      </c>
-      <c r="H49" s="28">
-        <f>H35-H47</f>
-        <v/>
-      </c>
-      <c r="I49" s="28">
-        <f>I35-I47</f>
-        <v/>
-      </c>
-      <c r="J49" s="28">
-        <f>J35-J47</f>
-        <v/>
-      </c>
-      <c r="K49" s="28">
-        <f>K35-K47</f>
-        <v/>
-      </c>
-      <c r="L49" s="28">
-        <f>L35-L47</f>
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>年末存款</t>
+        </is>
+      </c>
+      <c r="B49" s="22">
+        <f>B30+B48</f>
+        <v/>
+      </c>
+      <c r="C49" s="22">
+        <f>C30+C48</f>
+        <v/>
+      </c>
+      <c r="D49" s="22">
+        <f>D30+D48</f>
+        <v/>
+      </c>
+      <c r="E49" s="22">
+        <f>E30+E48</f>
+        <v/>
+      </c>
+      <c r="F49" s="22">
+        <f>F30+F48</f>
+        <v/>
+      </c>
+      <c r="H49" s="22">
+        <f>H30+H48</f>
+        <v/>
+      </c>
+      <c r="I49" s="22">
+        <f>I30+I48</f>
+        <v/>
+      </c>
+      <c r="J49" s="22">
+        <f>J30+J48</f>
+        <v/>
+      </c>
+      <c r="K49" s="22">
+        <f>K30+K48</f>
+        <v/>
+      </c>
+      <c r="L49" s="22">
+        <f>L30+L48</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>年末累计余额</t>
-        </is>
-      </c>
-      <c r="B50" s="22">
-        <f>B30+B49</f>
-        <v/>
-      </c>
-      <c r="C50" s="22">
-        <f>C30+C49</f>
-        <v/>
-      </c>
-      <c r="D50" s="22">
-        <f>D30+D49</f>
-        <v/>
-      </c>
-      <c r="E50" s="22">
-        <f>E30+E49</f>
-        <v/>
-      </c>
-      <c r="F50" s="22">
-        <f>F30+F49</f>
-        <v/>
-      </c>
-      <c r="H50" s="22">
-        <f>H30+H49</f>
-        <v/>
-      </c>
-      <c r="I50" s="22">
-        <f>I30+I49</f>
-        <v/>
-      </c>
-      <c r="J50" s="22">
-        <f>J30+J49</f>
-        <v/>
-      </c>
-      <c r="K50" s="22">
-        <f>K30+K49</f>
-        <v/>
-      </c>
-      <c r="L50" s="22">
-        <f>L30+L49</f>
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>年末剩余负债</t>
+        </is>
+      </c>
+      <c r="B50" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="28">
+        <f>SUMIFS('月度现金流（买房）'!R:R,'月度现金流（买房）'!B:B,2026,'月度现金流（买房）'!C:C,"12月")</f>
+        <v/>
+      </c>
+      <c r="I50" s="28">
+        <f>SUMIFS('月度现金流（买房）'!R:R,'月度现金流（买房）'!B:B,2027,'月度现金流（买房）'!C:C,"12月")</f>
+        <v/>
+      </c>
+      <c r="J50" s="28">
+        <f>SUMIFS('月度现金流（买房）'!R:R,'月度现金流（买房）'!B:B,2028,'月度现金流（买房）'!C:C,"12月")</f>
+        <v/>
+      </c>
+      <c r="K50" s="28">
+        <f>SUMIFS('月度现金流（买房）'!R:R,'月度现金流（买房）'!B:B,2029,'月度现金流（买房）'!C:C,"12月")</f>
+        <v/>
+      </c>
+      <c r="L50" s="28">
+        <f>SUMIFS('月度现金流（买房）'!R:R,'月度现金流（买房）'!B:B,2030,'月度现金流（买房）'!C:C,"12月")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>净存款</t>
+        </is>
+      </c>
+      <c r="B51" s="27">
+        <f>B49-B50</f>
+        <v/>
+      </c>
+      <c r="C51" s="27">
+        <f>C49-C50</f>
+        <v/>
+      </c>
+      <c r="D51" s="27">
+        <f>D49-D50</f>
+        <v/>
+      </c>
+      <c r="E51" s="27">
+        <f>E49-E50</f>
+        <v/>
+      </c>
+      <c r="F51" s="27">
+        <f>F49-F50</f>
+        <v/>
+      </c>
+      <c r="H51" s="27">
+        <f>H49-H50</f>
+        <v/>
+      </c>
+      <c r="I51" s="27">
+        <f>I49-I50</f>
+        <v/>
+      </c>
+      <c r="J51" s="27">
+        <f>J49-J50</f>
+        <v/>
+      </c>
+      <c r="K51" s="27">
+        <f>K49-K50</f>
+        <v/>
+      </c>
+      <c r="L51" s="27">
+        <f>L49-L50</f>
         <v/>
       </c>
     </row>
@@ -2076,7 +2151,7 @@
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A45:L45"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A36:L36"/>
